--- a/activities/03 - Find the Root Cause/data/A03-Data-Workbook.xlsx
+++ b/activities/03 - Find the Root Cause/data/A03-Data-Workbook.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v4</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v5</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>The Delay Reason column from the Lab 2 observation log, counted and ranked. This is the 'supplied Pareto chart' the lab's Step 5 refers to — the learner reads it rather than building it from scratch.</t>
+          <t>The Delay Reason column from the Activity 2 observation log, counted and ranked. This is the 'supplied Pareto chart' the lab's Step 5 refers to — the learner reads it rather than building it from scratch.</t>
         </is>
       </c>
     </row>

--- a/activities/03 - Find the Root Cause/data/A03-Data-Workbook.xlsx
+++ b/activities/03 - Find the Root Cause/data/A03-Data-Workbook.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v5</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v6</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>The Delay Reason column from the Activity 2 observation log, counted and ranked. This is the 'supplied Pareto chart' the lab's Step 5 refers to — the learner reads it rather than building it from scratch.</t>
+          <t>The Delay Reason column from the Activity 2 observation log, counted and ranked. This is the 'supplied Pareto chart' the activity's Step 5 refers to — the learner reads it rather than building it from scratch.</t>
         </is>
       </c>
     </row>

--- a/activities/03 - Find the Root Cause/data/A03-Data-Workbook.xlsx
+++ b/activities/03 - Find the Root Cause/data/A03-Data-Workbook.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v6</t>
+          <t>Certified Lean Six Sigma White Belt (CLSSWB) Training  ·  TGS-2025053210  ·  Version v7</t>
         </is>
       </c>
     </row>
